--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>228721</x:v>
+        <x:v>231721</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>457086</x:v>
+        <x:v>460086</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>5570</x:v>
+        <x:v>5810</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>18440</x:v>
+        <x:v>18800</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>18440</x:v>
+        <x:v>18800</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9271</x:v>
+        <x:v>9361</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>460086</x:v>
+        <x:v>461136</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>5810</x:v>
+        <x:v>5930</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>18800</x:v>
+        <x:v>18980</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>18800</x:v>
+        <x:v>18980</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9361</x:v>
+        <x:v>9391</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>461136</x:v>
+        <x:v>461646</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>5930</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>18980</x:v>
+        <x:v>19160</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>18980</x:v>
+        <x:v>19160</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23611</x:v>
+        <x:v>23671</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9391</x:v>
+        <x:v>9421</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>461646</x:v>
+        <x:v>462216</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23671</x:v>
+        <x:v>23791</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>462216</x:v>
+        <x:v>462336</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>231721</x:v>
+        <x:v>233221</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9421</x:v>
+        <x:v>9451</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>462336</x:v>
+        <x:v>463866</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>6050</x:v>
+        <x:v>8212</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>19160</x:v>
+        <x:v>23500</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>3174</x:v>
+        <x:v>4184</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2067,7 +2067,7 @@
       <x:c r="N19" s="56" t="s"/>
       <x:c r="O19" s="58" t="s"/>
       <x:c r="P19" s="60" t="n">
-        <x:v>7080</x:v>
+        <x:v>12720</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>20881</x:v>
+        <x:v>25441</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>233221</x:v>
+        <x:v>339661</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2139,7 +2139,7 @@
       <x:c r="N22" s="56" t="s"/>
       <x:c r="O22" s="58" t="s"/>
       <x:c r="P22" s="60" t="n">
-        <x:v>409.56</x:v>
+        <x:v>819.12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>19160</x:v>
+        <x:v>23500</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>111000</x:v>
+        <x:v>170856</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23791</x:v>
+        <x:v>34921</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>161</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>161</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2533,7 +2533,7 @@
       <x:c r="N39" s="56" t="s"/>
       <x:c r="O39" s="58" t="s"/>
       <x:c r="P39" s="60" t="n">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:16">
@@ -2605,7 +2605,7 @@
       <x:c r="N42" s="56" t="s"/>
       <x:c r="O42" s="58" t="s"/>
       <x:c r="P42" s="60" t="n">
-        <x:v>1550</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9451</x:v>
+        <x:v>14281</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>463866</x:v>
+        <x:v>669558</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>339661</x:v>
+        <x:v>340381</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>170856</x:v>
+        <x:v>171456</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>14281</x:v>
+        <x:v>14311</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>669558</x:v>
+        <x:v>670908</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>23500</x:v>
+        <x:v>24000</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>340381</x:v>
+        <x:v>341881</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>23500</x:v>
+        <x:v>24000</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>14311</x:v>
+        <x:v>14341</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>670908</x:v>
+        <x:v>673438</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>341881</x:v>
+        <x:v>342601</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>171456</x:v>
+        <x:v>172296</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>14341</x:v>
+        <x:v>14371</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>673438</x:v>
+        <x:v>675028</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>8212</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>24000</x:v>
+        <x:v>19660</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>4184</x:v>
+        <x:v>3174</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2067,7 +2067,7 @@
       <x:c r="N19" s="56" t="s"/>
       <x:c r="O19" s="58" t="s"/>
       <x:c r="P19" s="60" t="n">
-        <x:v>12720</x:v>
+        <x:v>7080</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>25441</x:v>
+        <x:v>20881</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>342601</x:v>
+        <x:v>236161</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2139,7 +2139,7 @@
       <x:c r="N22" s="56" t="s"/>
       <x:c r="O22" s="58" t="s"/>
       <x:c r="P22" s="60" t="n">
-        <x:v>819.12</x:v>
+        <x:v>409.56</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>24000</x:v>
+        <x:v>19660</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>172296</x:v>
+        <x:v>112680</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>34921</x:v>
+        <x:v>23791</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>241</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>241</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2533,7 +2533,7 @@
       <x:c r="N39" s="56" t="s"/>
       <x:c r="O39" s="58" t="s"/>
       <x:c r="P39" s="60" t="n">
-        <x:v>48</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:16">
@@ -2605,7 +2605,7 @@
       <x:c r="N42" s="56" t="s"/>
       <x:c r="O42" s="58" t="s"/>
       <x:c r="P42" s="60" t="n">
-        <x:v>2750</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>14371</x:v>
+        <x:v>9541</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>675028</x:v>
+        <x:v>469576</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>236161</x:v>
+        <x:v>237661</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9541</x:v>
+        <x:v>9571</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>469576</x:v>
+        <x:v>471106</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>237661</x:v>
+        <x:v>243661</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9571</x:v>
+        <x:v>9691</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>471106</x:v>
+        <x:v>477226</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>19660</x:v>
+        <x:v>21160</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>243661</x:v>
+        <x:v>248161</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>19660</x:v>
+        <x:v>21160</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9691</x:v>
+        <x:v>9781</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>477226</x:v>
+        <x:v>484816</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>21160</x:v>
+        <x:v>21660</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>248161</x:v>
+        <x:v>249661</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>21160</x:v>
+        <x:v>21660</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9781</x:v>
+        <x:v>9811</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>484816</x:v>
+        <x:v>487346</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>21660</x:v>
+        <x:v>21840</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2067,7 +2067,7 @@
       <x:c r="N19" s="56" t="s"/>
       <x:c r="O19" s="58" t="s"/>
       <x:c r="P19" s="60" t="n">
-        <x:v>7080</x:v>
+        <x:v>7560</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>21660</x:v>
+        <x:v>21840</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2605,7 +2605,7 @@
       <x:c r="N42" s="56" t="s"/>
       <x:c r="O42" s="58" t="s"/>
       <x:c r="P42" s="60" t="n">
-        <x:v>1550</x:v>
+        <x:v>1730</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9811</x:v>
+        <x:v>9841</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>487346</x:v>
+        <x:v>488396</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2067,7 +2067,7 @@
       <x:c r="N19" s="56" t="s"/>
       <x:c r="O19" s="58" t="s"/>
       <x:c r="P19" s="60" t="n">
-        <x:v>7560</x:v>
+        <x:v>8280</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9841</x:v>
+        <x:v>9901</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>488396</x:v>
+        <x:v>489176</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>21840</x:v>
+        <x:v>22340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>249661</x:v>
+        <x:v>251161</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>21840</x:v>
+        <x:v>22340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9901</x:v>
+        <x:v>9931</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>489176</x:v>
+        <x:v>491706</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>251161</x:v>
+        <x:v>251881</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>112680</x:v>
+        <x:v>113280</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>23791</x:v>
+        <x:v>24091</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>9931</x:v>
+        <x:v>10111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>491706</x:v>
+        <x:v>493506</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>113280</x:v>
+        <x:v>113520</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>493506</x:v>
+        <x:v>493746</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>22340</x:v>
+        <x:v>23340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>251881</x:v>
+        <x:v>255601</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>22340</x:v>
+        <x:v>23340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>113520</x:v>
+        <x:v>114516</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24091</x:v>
+        <x:v>24271</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10111</x:v>
+        <x:v>10231</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>493746</x:v>
+        <x:v>500762</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24271</x:v>
+        <x:v>24471</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>500762</x:v>
+        <x:v>500962</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>23340</x:v>
+        <x:v>24340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>255601</x:v>
+        <x:v>259321</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>23340</x:v>
+        <x:v>24340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>114516</x:v>
+        <x:v>114984</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24471</x:v>
+        <x:v>24411</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10231</x:v>
+        <x:v>10321</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>500962</x:v>
+        <x:v>507180</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>114984</x:v>
+        <x:v>115224</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>507180</x:v>
+        <x:v>507420</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>259321</x:v>
+        <x:v>268681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>115224</x:v>
+        <x:v>123024</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24411</x:v>
+        <x:v>24591</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10321</x:v>
+        <x:v>10741</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>507420</x:v>
+        <x:v>525180</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>268681</x:v>
+        <x:v>271681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>123024</x:v>
+        <x:v>123504</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10741</x:v>
+        <x:v>10801</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>525180</x:v>
+        <x:v>528720</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>123504</x:v>
+        <x:v>123744</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>528720</x:v>
+        <x:v>528960</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>24340</x:v>
+        <x:v>26340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>271681</x:v>
+        <x:v>277681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>24340</x:v>
+        <x:v>26340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>123744</x:v>
+        <x:v>123876</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24591</x:v>
+        <x:v>24651</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10801</x:v>
+        <x:v>10921</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>528960</x:v>
+        <x:v>539272</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>277681</x:v>
+        <x:v>279181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10921</x:v>
+        <x:v>10951</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>539272</x:v>
+        <x:v>540802</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24651</x:v>
+        <x:v>24711</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10951</x:v>
+        <x:v>10981</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>540802</x:v>
+        <x:v>540892</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24711</x:v>
+        <x:v>24831</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>540892</x:v>
+        <x:v>541012</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>6050</x:v>
+        <x:v>6170</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>26340</x:v>
+        <x:v>26520</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>279181</x:v>
+        <x:v>282181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>26340</x:v>
+        <x:v>26520</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>10981</x:v>
+        <x:v>11071</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>541012</x:v>
+        <x:v>544582</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>282181</x:v>
+        <x:v>283681</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11071</x:v>
+        <x:v>11101</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>544582</x:v>
+        <x:v>546112</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>6170</x:v>
+        <x:v>6266</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>26520</x:v>
+        <x:v>26700</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>26520</x:v>
+        <x:v>26700</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>546112</x:v>
+        <x:v>546568</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>6266</x:v>
+        <x:v>6290</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11101</x:v>
+        <x:v>11131</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>546568</x:v>
+        <x:v>546622</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>26700</x:v>
+        <x:v>26740</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>26700</x:v>
+        <x:v>26740</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>24831</x:v>
+        <x:v>24951</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>161</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>161</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11131</x:v>
+        <x:v>11191</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>546622</x:v>
+        <x:v>546962</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:IX.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:IX.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>283681</x:v>
+        <x:v>285181</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>11191</x:v>
+        <x:v>11221</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>546962</x:v>
+        <x:v>548492</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">
